--- a/MORITZ APA 136.xlsx
+++ b/MORITZ APA 136.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/moriheidtmann/Documents/Work/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/moriheidtmann/Documents/Work/Playwrite_VS_Extention/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49210AAF-23D3-6C43-A60E-0B2D6A541619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9F69131-C58E-594C-A453-4C81EAD3FC11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3856" uniqueCount="1073">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3861" uniqueCount="1077">
   <si>
     <t>ae_authorisationNotificationDateStr</t>
   </si>
@@ -3222,9 +3222,6 @@
     <t>NASDAQ Baltic</t>
   </si>
   <si>
-    <t>CBOE &amp; Euronext&amp; ICE</t>
-  </si>
-  <si>
     <t>ICE is for startups i dont think they have a personal data vendor</t>
   </si>
   <si>
@@ -3234,9 +3231,6 @@
     <t>ziemlich sicher</t>
   </si>
   <si>
-    <t>???</t>
-  </si>
-  <si>
     <t>https://www.bsse.sk/bcpb/en/market-data/pre-trade-and-post-trade-data/</t>
   </si>
   <si>
@@ -3256,13 +3250,31 @@
   </si>
   <si>
     <t>Alternatively: https://www.bse-sofia.bg/en/apa-trading-data</t>
+  </si>
+  <si>
+    <t>ATHEX provides comprehensive Pre &amp; Post-Trade transparency services, including Real Time Data Feed &amp; Reference Data. Markets supported are Athens Stock Exchange, Cyprus Stock Exchange and Hellenic Energy Exchange. ATHEX also offers data feed for APA@ATHEX.</t>
+  </si>
+  <si>
+    <t>https://www.athexgroup.gr/en/solutions-and-services/technology/data-feed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATHEX </t>
+  </si>
+  <si>
+    <t>Trading on Malta Stock Exchange takes place through the Xetra trading system. Xetra is a trading system operated by Deutsche Bõrse AG and offers trading functionality in line with international standards making it easier for international participation.</t>
+  </si>
+  <si>
+    <t>https://www.borzamalta.com.mt/trading</t>
+  </si>
+  <si>
+    <t>CBOE &amp; Euronext&amp; ICE&amp; CME</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -3303,6 +3315,23 @@
       <sz val="11"/>
       <color theme="9"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="9"/>
+      <name val="Manrope"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF00B050"/>
+      <name val="Helvetica Neue"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -3387,7 +3416,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -3401,13 +3430,12 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -3714,7 +3742,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AX140"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="29.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
@@ -3767,7 +3795,7 @@
     <col min="50" max="50" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:50">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3919,7 +3947,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:50">
       <c r="A2" t="s">
         <v>50</v>
       </c>
@@ -3987,7 +4015,7 @@
         <v>1.8226054250689987E+18</v>
       </c>
     </row>
-    <row r="3" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:50">
       <c r="A3" t="s">
         <v>68</v>
       </c>
@@ -4055,7 +4083,7 @@
         <v>1.8226054340563436E+18</v>
       </c>
     </row>
-    <row r="4" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:50">
       <c r="A4" t="s">
         <v>50</v>
       </c>
@@ -4123,7 +4151,7 @@
         <v>1.8226055766521938E+18</v>
       </c>
     </row>
-    <row r="5" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:50">
       <c r="A5" t="s">
         <v>68</v>
       </c>
@@ -4191,7 +4219,7 @@
         <v>1.8226056627528663E+18</v>
       </c>
     </row>
-    <row r="6" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:50">
       <c r="A6" t="s">
         <v>68</v>
       </c>
@@ -4259,7 +4287,7 @@
         <v>1.8226056628409467E+18</v>
       </c>
     </row>
-    <row r="7" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:50">
       <c r="A7" t="s">
         <v>92</v>
       </c>
@@ -4327,7 +4355,7 @@
         <v>1.8226053832706621E+18</v>
       </c>
     </row>
-    <row r="8" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:50">
       <c r="A8" t="s">
         <v>68</v>
       </c>
@@ -4395,7 +4423,7 @@
         <v>1.8226054212416963E+18</v>
       </c>
     </row>
-    <row r="9" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:50">
       <c r="A9" t="s">
         <v>68</v>
       </c>
@@ -4463,7 +4491,7 @@
         <v>1.8226054303768904E+18</v>
       </c>
     </row>
-    <row r="10" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:50">
       <c r="A10" t="s">
         <v>117</v>
       </c>
@@ -4531,7 +4559,7 @@
         <v>1.8226054731965399E+18</v>
       </c>
     </row>
-    <row r="11" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:50">
       <c r="A11" t="s">
         <v>68</v>
       </c>
@@ -4599,7 +4627,7 @@
         <v>1.8226055112483144E+18</v>
       </c>
     </row>
-    <row r="12" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:50">
       <c r="A12" t="s">
         <v>132</v>
       </c>
@@ -4667,7 +4695,7 @@
         <v>1.8226055329915863E+18</v>
       </c>
     </row>
-    <row r="13" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:50">
       <c r="A13" t="s">
         <v>68</v>
       </c>
@@ -4735,7 +4763,7 @@
         <v>1.8226055590182912E+18</v>
       </c>
     </row>
-    <row r="14" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:50">
       <c r="A14" t="s">
         <v>68</v>
       </c>
@@ -4803,7 +4831,7 @@
         <v>1.8226055962133791E+18</v>
       </c>
     </row>
-    <row r="15" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:50">
       <c r="A15" t="s">
         <v>68</v>
       </c>
@@ -4871,7 +4899,7 @@
         <v>1.8226056091286897E+18</v>
       </c>
     </row>
-    <row r="16" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:50">
       <c r="A16" t="s">
         <v>68</v>
       </c>
@@ -4939,7 +4967,7 @@
         <v>1.8226056092765389E+18</v>
       </c>
     </row>
-    <row r="17" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:49">
       <c r="A17" t="s">
         <v>68</v>
       </c>
@@ -5007,7 +5035,7 @@
         <v>1.8226056369264394E+18</v>
       </c>
     </row>
-    <row r="18" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:49">
       <c r="A18" t="s">
         <v>68</v>
       </c>
@@ -5075,7 +5103,7 @@
         <v>1.8226056452563272E+18</v>
       </c>
     </row>
-    <row r="19" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:49">
       <c r="A19" t="s">
         <v>117</v>
       </c>
@@ -5143,7 +5171,7 @@
         <v>1.8226055080375747E+18</v>
       </c>
     </row>
-    <row r="20" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:49">
       <c r="A20" t="s">
         <v>117</v>
       </c>
@@ -5211,7 +5239,7 @@
         <v>1.8226056680156692E+18</v>
       </c>
     </row>
-    <row r="21" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:49">
       <c r="A21" t="s">
         <v>173</v>
       </c>
@@ -5279,7 +5307,7 @@
         <v>1.8226055139525919E+18</v>
       </c>
     </row>
-    <row r="22" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:49">
       <c r="A22" t="s">
         <v>173</v>
       </c>
@@ -5347,7 +5375,7 @@
         <v>1.82260557087454E+18</v>
       </c>
     </row>
-    <row r="23" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:49">
       <c r="A23" t="s">
         <v>189</v>
       </c>
@@ -5415,7 +5443,7 @@
         <v>1.8226056276308132E+18</v>
       </c>
     </row>
-    <row r="24" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:49">
       <c r="A24" t="s">
         <v>197</v>
       </c>
@@ -5483,7 +5511,7 @@
         <v>1.8226054214860145E+18</v>
       </c>
     </row>
-    <row r="25" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:49">
       <c r="A25" t="s">
         <v>210</v>
       </c>
@@ -5551,7 +5579,7 @@
         <v>1.8226054926140703E+18</v>
       </c>
     </row>
-    <row r="26" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:49">
       <c r="A26" t="s">
         <v>219</v>
       </c>
@@ -5619,7 +5647,7 @@
         <v>1.8226056588175606E+18</v>
       </c>
     </row>
-    <row r="27" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:49">
       <c r="A27" t="s">
         <v>231</v>
       </c>
@@ -5687,7 +5715,7 @@
         <v>1.8226054309431214E+18</v>
       </c>
     </row>
-    <row r="28" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:49">
       <c r="A28" t="s">
         <v>50</v>
       </c>
@@ -5755,7 +5783,7 @@
         <v>1.8226053834269E+18</v>
       </c>
     </row>
-    <row r="29" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:49">
       <c r="A29" t="s">
         <v>50</v>
       </c>
@@ -5823,7 +5851,7 @@
         <v>1.8226054994906317E+18</v>
       </c>
     </row>
-    <row r="30" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:49">
       <c r="A30" t="s">
         <v>50</v>
       </c>
@@ -5891,7 +5919,7 @@
         <v>1.8226054994130371E+18</v>
       </c>
     </row>
-    <row r="31" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:49">
       <c r="A31" t="s">
         <v>50</v>
       </c>
@@ -5959,7 +5987,7 @@
         <v>1.8226055025661051E+18</v>
       </c>
     </row>
-    <row r="32" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:49">
       <c r="A32" t="s">
         <v>50</v>
       </c>
@@ -6027,7 +6055,7 @@
         <v>1.8226055026416026E+18</v>
       </c>
     </row>
-    <row r="33" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:49">
       <c r="A33" t="s">
         <v>50</v>
       </c>
@@ -6095,7 +6123,7 @@
         <v>1.8226055024801219E+18</v>
       </c>
     </row>
-    <row r="34" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:49">
       <c r="A34" t="s">
         <v>50</v>
       </c>
@@ -6163,7 +6191,7 @@
         <v>1.8226055024035758E+18</v>
       </c>
     </row>
-    <row r="35" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:49">
       <c r="A35" t="s">
         <v>50</v>
       </c>
@@ -6231,7 +6259,7 @@
         <v>1.8226055027244401E+18</v>
       </c>
     </row>
-    <row r="36" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:49">
       <c r="A36" t="s">
         <v>50</v>
       </c>
@@ -6299,7 +6327,7 @@
         <v>1.8226055029047951E+18</v>
       </c>
     </row>
-    <row r="37" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:49">
       <c r="A37" t="s">
         <v>50</v>
       </c>
@@ -6367,7 +6395,7 @@
         <v>1.8226055027957432E+18</v>
       </c>
     </row>
-    <row r="38" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:49">
       <c r="A38" t="s">
         <v>50</v>
       </c>
@@ -6435,7 +6463,7 @@
         <v>1.8226055301405082E+18</v>
       </c>
     </row>
-    <row r="39" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:49">
       <c r="A39" t="s">
         <v>50</v>
       </c>
@@ -6503,7 +6531,7 @@
         <v>1.8226056720904356E+18</v>
       </c>
     </row>
-    <row r="40" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:49">
       <c r="A40" t="s">
         <v>311</v>
       </c>
@@ -6571,7 +6599,7 @@
         <v>1.8226056369977426E+18</v>
       </c>
     </row>
-    <row r="41" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:49">
       <c r="A41" t="s">
         <v>68</v>
       </c>
@@ -6639,7 +6667,7 @@
         <v>1.8226056773721129E+18</v>
       </c>
     </row>
-    <row r="42" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:49">
       <c r="A42" t="s">
         <v>68</v>
       </c>
@@ -6707,7 +6735,7 @@
         <v>1.8226056772892754E+18</v>
       </c>
     </row>
-    <row r="43" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:49">
       <c r="A43" t="s">
         <v>337</v>
       </c>
@@ -6775,7 +6803,7 @@
         <v>1.8226055233205699E+18</v>
       </c>
     </row>
-    <row r="44" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:49">
       <c r="A44" t="s">
         <v>68</v>
       </c>
@@ -6843,7 +6871,7 @@
         <v>1.8226054253311427E+18</v>
       </c>
     </row>
-    <row r="45" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:49">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -6911,7 +6939,7 @@
         <v>1.8226055194618102E+18</v>
       </c>
     </row>
-    <row r="46" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:49">
       <c r="A46" t="s">
         <v>50</v>
       </c>
@@ -6982,7 +7010,7 @@
         <v>1.8226056504016896E+18</v>
       </c>
     </row>
-    <row r="47" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:49">
       <c r="A47" t="s">
         <v>50</v>
       </c>
@@ -7053,7 +7081,7 @@
         <v>1.8226056544858931E+18</v>
       </c>
     </row>
-    <row r="48" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:49">
       <c r="A48" t="s">
         <v>375</v>
       </c>
@@ -7121,7 +7149,7 @@
         <v>1.8226056814405878E+18</v>
       </c>
     </row>
-    <row r="49" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:49">
       <c r="A49" t="s">
         <v>385</v>
       </c>
@@ -7189,7 +7217,7 @@
         <v>1.8226053876935557E+18</v>
       </c>
     </row>
-    <row r="50" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:49">
       <c r="A50" t="s">
         <v>397</v>
       </c>
@@ -7257,7 +7285,7 @@
         <v>1.822605523550208E+18</v>
       </c>
     </row>
-    <row r="51" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:49">
       <c r="A51" t="s">
         <v>407</v>
       </c>
@@ -7325,7 +7353,7 @@
         <v>1.8226055308797542E+18</v>
       </c>
     </row>
-    <row r="52" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:49">
       <c r="A52" t="s">
         <v>415</v>
       </c>
@@ -7393,7 +7421,7 @@
         <v>1.8226055397926502E+18</v>
       </c>
     </row>
-    <row r="53" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:49">
       <c r="A53" t="s">
         <v>425</v>
       </c>
@@ -7461,7 +7489,7 @@
         <v>1.8226056505254216E+18</v>
       </c>
     </row>
-    <row r="54" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:49">
       <c r="A54" t="s">
         <v>436</v>
       </c>
@@ -7529,7 +7557,7 @@
         <v>1.8226056816146514E+18</v>
       </c>
     </row>
-    <row r="55" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:49">
       <c r="A55" t="s">
         <v>448</v>
       </c>
@@ -7597,7 +7625,7 @@
         <v>1.8226053840885514E+18</v>
       </c>
     </row>
-    <row r="56" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:49">
       <c r="A56" t="s">
         <v>460</v>
       </c>
@@ -7665,7 +7693,7 @@
         <v>1.822605493003092E+18</v>
       </c>
     </row>
-    <row r="57" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:49">
       <c r="A57" t="s">
         <v>448</v>
       </c>
@@ -7733,7 +7761,7 @@
         <v>1.8226054995692749E+18</v>
       </c>
     </row>
-    <row r="58" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:49">
       <c r="A58" t="s">
         <v>448</v>
       </c>
@@ -7801,7 +7829,7 @@
         <v>1.8226055310401864E+18</v>
       </c>
     </row>
-    <row r="59" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:49">
       <c r="A59" t="s">
         <v>448</v>
       </c>
@@ -7869,7 +7897,7 @@
         <v>1.8226055399929283E+18</v>
       </c>
     </row>
-    <row r="60" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:49">
       <c r="A60" t="s">
         <v>448</v>
       </c>
@@ -7937,7 +7965,7 @@
         <v>1.8226056428540396E+18</v>
       </c>
     </row>
-    <row r="61" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:49">
       <c r="A61" t="s">
         <v>479</v>
       </c>
@@ -8005,7 +8033,7 @@
         <v>1.8226056852574044E+18</v>
       </c>
     </row>
-    <row r="62" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:49">
       <c r="A62" t="s">
         <v>448</v>
       </c>
@@ -8073,7 +8101,7 @@
         <v>1.822605688411521E+18</v>
       </c>
     </row>
-    <row r="63" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:49">
       <c r="A63" t="s">
         <v>489</v>
       </c>
@@ -8141,7 +8169,7 @@
         <v>1.8226053988682301E+18</v>
       </c>
     </row>
-    <row r="64" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:49">
       <c r="A64" t="s">
         <v>501</v>
       </c>
@@ -8209,7 +8237,7 @@
         <v>1.8226055123304448E+18</v>
       </c>
     </row>
-    <row r="65" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:49">
       <c r="A65" t="s">
         <v>510</v>
       </c>
@@ -8277,7 +8305,7 @@
         <v>1.8226056546400338E+18</v>
       </c>
     </row>
-    <row r="66" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:49">
       <c r="A66" t="s">
         <v>517</v>
       </c>
@@ -8345,7 +8373,7 @@
         <v>1.8226053990422938E+18</v>
       </c>
     </row>
-    <row r="67" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:49">
       <c r="A67" t="s">
         <v>517</v>
       </c>
@@ -8413,7 +8441,7 @@
         <v>1.8226054934120366E+18</v>
       </c>
     </row>
-    <row r="68" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:49">
       <c r="A68" t="s">
         <v>517</v>
       </c>
@@ -8481,7 +8509,7 @@
         <v>1.822605493334442E+18</v>
       </c>
     </row>
-    <row r="69" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:49">
       <c r="A69" t="s">
         <v>517</v>
       </c>
@@ -8549,7 +8577,7 @@
         <v>1.8226055031816192E+18</v>
       </c>
     </row>
-    <row r="70" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:49">
       <c r="A70" t="s">
         <v>517</v>
       </c>
@@ -8617,7 +8645,7 @@
         <v>1.8226055082095411E+18</v>
       </c>
     </row>
-    <row r="71" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:49">
       <c r="A71" t="s">
         <v>517</v>
       </c>
@@ -8685,7 +8713,7 @@
         <v>1.822605536002048E+18</v>
       </c>
     </row>
-    <row r="72" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:49">
       <c r="A72" t="s">
         <v>517</v>
       </c>
@@ -8753,7 +8781,7 @@
         <v>1.8226056331232543E+18</v>
       </c>
     </row>
-    <row r="73" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:49">
       <c r="A73" t="s">
         <v>517</v>
       </c>
@@ -8821,7 +8849,7 @@
         <v>1.8226056332773949E+18</v>
       </c>
     </row>
-    <row r="74" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:49">
       <c r="A74" t="s">
         <v>517</v>
       </c>
@@ -8889,7 +8917,7 @@
         <v>1.8226056429452657E+18</v>
       </c>
     </row>
-    <row r="75" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:49">
       <c r="A75" t="s">
         <v>517</v>
       </c>
@@ -8957,7 +8985,7 @@
         <v>1.8226056453318246E+18</v>
       </c>
     </row>
-    <row r="76" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:49">
       <c r="A76" t="s">
         <v>517</v>
       </c>
@@ -9025,7 +9053,7 @@
         <v>1.8226056454031278E+18</v>
       </c>
     </row>
-    <row r="77" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:49">
       <c r="A77" t="s">
         <v>517</v>
       </c>
@@ -9093,7 +9121,7 @@
         <v>1.8226056598126592E+18</v>
       </c>
     </row>
-    <row r="78" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:49">
       <c r="A78" t="s">
         <v>573</v>
       </c>
@@ -9161,7 +9189,7 @@
         <v>1.8226056882647204E+18</v>
       </c>
     </row>
-    <row r="79" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:49">
       <c r="A79" t="s">
         <v>583</v>
       </c>
@@ -9232,7 +9260,7 @@
         <v>1.8226055288906056E+18</v>
       </c>
     </row>
-    <row r="80" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:49">
       <c r="A80" t="s">
         <v>592</v>
       </c>
@@ -9303,7 +9331,7 @@
         <v>1.8226055424077988E+18</v>
       </c>
     </row>
-    <row r="81" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:49">
       <c r="A81" t="s">
         <v>599</v>
       </c>
@@ -9371,7 +9399,7 @@
         <v>1.8226056639388058E+18</v>
       </c>
     </row>
-    <row r="82" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:49">
       <c r="A82" t="s">
         <v>448</v>
       </c>
@@ -9442,7 +9470,7 @@
         <v>1.822605612637225E+18</v>
       </c>
     </row>
-    <row r="83" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:49">
       <c r="A83" t="s">
         <v>448</v>
       </c>
@@ -9513,7 +9541,7 @@
         <v>1.8226056262571786E+18</v>
       </c>
     </row>
-    <row r="84" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:49">
       <c r="A84" t="s">
         <v>517</v>
       </c>
@@ -9581,7 +9609,7 @@
         <v>1.8226054891191665E+18</v>
       </c>
     </row>
-    <row r="85" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:49">
       <c r="A85" t="s">
         <v>627</v>
       </c>
@@ -9649,7 +9677,7 @@
         <v>1.8226054441939763E+18</v>
       </c>
     </row>
-    <row r="86" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:49">
       <c r="A86" t="s">
         <v>627</v>
       </c>
@@ -9717,7 +9745,7 @@
         <v>1.8226055040991232E+18</v>
       </c>
     </row>
-    <row r="87" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:49">
       <c r="A87" t="s">
         <v>645</v>
       </c>
@@ -9785,7 +9813,7 @@
         <v>1.8226054447518188E+18</v>
       </c>
     </row>
-    <row r="88" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:49">
       <c r="A88" t="s">
         <v>68</v>
       </c>
@@ -9853,7 +9881,7 @@
         <v>1.8226054879720243E+18</v>
       </c>
     </row>
-    <row r="89" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:49">
       <c r="A89" t="s">
         <v>668</v>
       </c>
@@ -9921,7 +9949,7 @@
         <v>1.8226056526047478E+18</v>
       </c>
     </row>
-    <row r="90" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:49">
       <c r="A90" t="s">
         <v>680</v>
       </c>
@@ -9989,7 +10017,7 @@
         <v>1.82260561181619E+18</v>
       </c>
     </row>
-    <row r="91" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:49">
       <c r="A91" t="s">
         <v>688</v>
       </c>
@@ -10057,7 +10085,7 @@
         <v>1.8226056611003105E+18</v>
       </c>
     </row>
-    <row r="92" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:49">
       <c r="A92" t="s">
         <v>694</v>
       </c>
@@ -10125,7 +10153,7 @@
         <v>1.8226056527504998E+18</v>
       </c>
     </row>
-    <row r="93" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:49">
       <c r="A93" t="s">
         <v>704</v>
       </c>
@@ -10193,7 +10221,7 @@
         <v>1.8226056529350492E+18</v>
       </c>
     </row>
-    <row r="94" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:49">
       <c r="A94" t="s">
         <v>704</v>
       </c>
@@ -10261,7 +10289,7 @@
         <v>1.8226056248520868E+18</v>
       </c>
     </row>
-    <row r="95" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:49">
       <c r="A95" t="s">
         <v>704</v>
       </c>
@@ -10329,7 +10357,7 @@
         <v>1.8226056249286328E+18</v>
       </c>
     </row>
-    <row r="96" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:49">
       <c r="A96" t="s">
         <v>704</v>
       </c>
@@ -10397,7 +10425,7 @@
         <v>1.8226056250030817E+18</v>
       </c>
     </row>
-    <row r="97" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:49">
       <c r="A97" t="s">
         <v>725</v>
       </c>
@@ -10465,7 +10493,7 @@
         <v>1.8226054102945628E+18</v>
       </c>
     </row>
-    <row r="98" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:49">
       <c r="A98" t="s">
         <v>733</v>
       </c>
@@ -10533,7 +10561,7 @@
         <v>1.8226055121637212E+18</v>
       </c>
     </row>
-    <row r="99" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:49">
       <c r="A99" t="s">
         <v>407</v>
       </c>
@@ -10601,7 +10629,7 @@
         <v>1.8226055478970941E+18</v>
       </c>
     </row>
-    <row r="100" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:49">
       <c r="A100" t="s">
         <v>747</v>
       </c>
@@ -10669,7 +10697,7 @@
         <v>1.8226055656222228E+18</v>
       </c>
     </row>
-    <row r="101" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:49">
       <c r="A101" t="s">
         <v>68</v>
       </c>
@@ -10737,7 +10765,7 @@
         <v>1.8226056721669816E+18</v>
       </c>
     </row>
-    <row r="102" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:49">
       <c r="A102" t="s">
         <v>68</v>
       </c>
@@ -10805,7 +10833,7 @@
         <v>1.8226056880885596E+18</v>
       </c>
     </row>
-    <row r="103" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:49">
       <c r="A103" t="s">
         <v>50</v>
       </c>
@@ -10873,7 +10901,7 @@
         <v>1.8226057451615027E+18</v>
       </c>
     </row>
-    <row r="104" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:49">
       <c r="A104" t="s">
         <v>50</v>
       </c>
@@ -10941,7 +10969,7 @@
         <v>1.8226057453282263E+18</v>
       </c>
     </row>
-    <row r="105" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:49">
       <c r="A105" t="s">
         <v>50</v>
       </c>
@@ -11009,7 +11037,7 @@
         <v>1.8226057455012413E+18</v>
       </c>
     </row>
-    <row r="106" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:49">
       <c r="A106" t="s">
         <v>68</v>
       </c>
@@ -11077,7 +11105,7 @@
         <v>1.8226054126465188E+18</v>
       </c>
     </row>
-    <row r="107" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:49">
       <c r="A107" t="s">
         <v>68</v>
       </c>
@@ -11145,7 +11173,7 @@
         <v>1.8226056291879485E+18</v>
       </c>
     </row>
-    <row r="108" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:49">
       <c r="A108" t="s">
         <v>800</v>
       </c>
@@ -11213,7 +11241,7 @@
         <v>1.8226056986047283E+18</v>
       </c>
     </row>
-    <row r="109" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:49">
       <c r="A109" t="s">
         <v>68</v>
       </c>
@@ -11284,7 +11312,7 @@
         <v>1.8226057301479916E+18</v>
       </c>
     </row>
-    <row r="110" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:49">
       <c r="A110" t="s">
         <v>50</v>
       </c>
@@ -11352,7 +11380,7 @@
         <v>1.8226055765840364E+18</v>
       </c>
     </row>
-    <row r="111" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:49">
       <c r="A111" t="s">
         <v>50</v>
       </c>
@@ -11420,7 +11448,7 @@
         <v>1.8226056585648538E+18</v>
       </c>
     </row>
-    <row r="112" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:49">
       <c r="A112" t="s">
         <v>827</v>
       </c>
@@ -11488,7 +11516,7 @@
         <v>1.8226058367210619E+18</v>
       </c>
     </row>
-    <row r="113" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:49">
       <c r="A113" t="s">
         <v>800</v>
       </c>
@@ -11556,7 +11584,7 @@
         <v>1.8226056933251482E+18</v>
       </c>
     </row>
-    <row r="114" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:49">
       <c r="A114" t="s">
         <v>840</v>
       </c>
@@ -11624,7 +11652,7 @@
         <v>1.8226057197440205E+18</v>
       </c>
     </row>
-    <row r="115" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:49">
       <c r="A115" t="s">
         <v>173</v>
       </c>
@@ -11692,7 +11720,7 @@
         <v>1.8226053983963709E+18</v>
       </c>
     </row>
-    <row r="116" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:49">
       <c r="A116" t="s">
         <v>851</v>
       </c>
@@ -11760,7 +11788,7 @@
         <v>1.8226055464752251E+18</v>
       </c>
     </row>
-    <row r="117" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:49">
       <c r="A117" t="s">
         <v>857</v>
       </c>
@@ -11828,7 +11856,7 @@
         <v>1.8226053864059044E+18</v>
       </c>
     </row>
-    <row r="118" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:49">
       <c r="A118" t="s">
         <v>869</v>
       </c>
@@ -11893,7 +11921,7 @@
         <v>1.8226057954994422E+18</v>
       </c>
     </row>
-    <row r="119" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:49">
       <c r="A119" t="s">
         <v>397</v>
       </c>
@@ -11961,7 +11989,7 @@
         <v>1.8226055337004237E+18</v>
       </c>
     </row>
-    <row r="120" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:49">
       <c r="A120" t="s">
         <v>881</v>
       </c>
@@ -12029,7 +12057,7 @@
         <v>1.8226056780400558E+18</v>
       </c>
     </row>
-    <row r="121" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:49">
       <c r="A121" t="s">
         <v>889</v>
       </c>
@@ -12097,7 +12125,7 @@
         <v>1.822605891634987E+18</v>
       </c>
     </row>
-    <row r="122" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:49">
       <c r="A122" t="s">
         <v>50</v>
       </c>
@@ -12165,7 +12193,7 @@
         <v>1.822605383510786E+18</v>
       </c>
     </row>
-    <row r="123" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:49">
       <c r="A123" t="s">
         <v>50</v>
       </c>
@@ -12233,7 +12261,7 @@
         <v>1.822605404047147E+18</v>
       </c>
     </row>
-    <row r="124" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:49">
       <c r="A124" t="s">
         <v>50</v>
       </c>
@@ -12301,7 +12329,7 @@
         <v>1.8226056590597816E+18</v>
       </c>
     </row>
-    <row r="125" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:49">
       <c r="A125" t="s">
         <v>50</v>
       </c>
@@ -12369,7 +12397,7 @@
         <v>1.8226056591363277E+18</v>
       </c>
     </row>
-    <row r="126" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:49">
       <c r="A126" t="s">
         <v>915</v>
       </c>
@@ -12437,7 +12465,7 @@
         <v>1.8226053833472082E+18</v>
       </c>
     </row>
-    <row r="127" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:49">
       <c r="A127" t="s">
         <v>923</v>
       </c>
@@ -12502,7 +12530,7 @@
         <v>1.8226058803659407E+18</v>
       </c>
     </row>
-    <row r="128" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:49">
       <c r="A128" t="s">
         <v>923</v>
       </c>
@@ -12567,7 +12595,7 @@
         <v>1.8226058806050161E+18</v>
       </c>
     </row>
-    <row r="129" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:49">
       <c r="A129" t="s">
         <v>923</v>
       </c>
@@ -12632,7 +12660,7 @@
         <v>1.8226059113188557E+18</v>
       </c>
     </row>
-    <row r="130" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:49">
       <c r="A130" t="s">
         <v>50</v>
       </c>
@@ -12700,7 +12728,7 @@
         <v>1.822605487347073E+18</v>
       </c>
     </row>
-    <row r="131" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:49">
       <c r="A131" t="s">
         <v>945</v>
       </c>
@@ -12768,7 +12796,7 @@
         <v>1.8226055263215944E+18</v>
       </c>
     </row>
-    <row r="132" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:49">
       <c r="A132" t="s">
         <v>50</v>
       </c>
@@ -12836,7 +12864,7 @@
         <v>1.822605659217068E+18</v>
       </c>
     </row>
-    <row r="133" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:49">
       <c r="A133" t="s">
         <v>957</v>
       </c>
@@ -12904,7 +12932,7 @@
         <v>1.8226058766319616E+18</v>
       </c>
     </row>
-    <row r="134" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:49">
       <c r="A134" t="s">
         <v>963</v>
       </c>
@@ -12972,7 +13000,7 @@
         <v>1.8226059474129388E+18</v>
       </c>
     </row>
-    <row r="135" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:49">
       <c r="A135" t="s">
         <v>969</v>
       </c>
@@ -13040,7 +13068,7 @@
         <v>1.8226060105330196E+18</v>
       </c>
     </row>
-    <row r="136" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:49">
       <c r="A136" t="s">
         <v>963</v>
       </c>
@@ -13108,7 +13136,7 @@
         <v>1.8226059427216097E+18</v>
       </c>
     </row>
-    <row r="137" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:49">
       <c r="A137" t="s">
         <v>969</v>
       </c>
@@ -13173,7 +13201,7 @@
         <v>1.8226059906782331E+18</v>
       </c>
     </row>
-    <row r="138" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:49">
       <c r="A138" t="s">
         <v>987</v>
       </c>
@@ -13241,7 +13269,7 @@
         <v>1.8258007207108936E+18</v>
       </c>
     </row>
-    <row r="139" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:49">
       <c r="A139" t="s">
         <v>997</v>
       </c>
@@ -13309,7 +13337,7 @@
         <v>1.8285186110424351E+18</v>
       </c>
     </row>
-    <row r="140" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:49">
       <c r="A140" t="s">
         <v>1005</v>
       </c>
@@ -13387,7 +13415,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41B1068A-70D8-5141-B56A-F887E4222AFE}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
@@ -13395,7 +13423,7 @@
     <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" s="2" customFormat="1">
       <c r="A1" s="2" t="s">
         <v>70</v>
       </c>
@@ -13415,7 +13443,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" s="2" customFormat="1">
       <c r="A2" s="2" t="s">
         <v>84</v>
       </c>
@@ -13432,7 +13460,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" s="2" customFormat="1">
       <c r="A3" s="2" t="s">
         <v>88</v>
       </c>
@@ -13452,7 +13480,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" s="2" customFormat="1">
       <c r="A4" s="2" t="s">
         <v>84</v>
       </c>
@@ -13477,7 +13505,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{190D282D-A498-5040-B7ED-BB0A4708E39A}">
   <dimension ref="A1:F25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="81.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="77.83203125" bestFit="1" customWidth="1"/>
@@ -13486,7 +13514,7 @@
     <col min="6" max="6" width="255.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -13506,7 +13534,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" s="2" customFormat="1">
       <c r="A2" s="2" t="s">
         <v>244</v>
       </c>
@@ -13523,7 +13551,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" s="2" customFormat="1">
       <c r="A3" s="2" t="s">
         <v>253</v>
       </c>
@@ -13537,7 +13565,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" s="2" customFormat="1">
       <c r="A4" s="2" t="s">
         <v>259</v>
       </c>
@@ -13551,7 +13579,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="5" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" s="2" customFormat="1">
       <c r="A5" s="2" t="s">
         <v>263</v>
       </c>
@@ -13565,7 +13593,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="6" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" s="2" customFormat="1">
       <c r="A6" s="2" t="s">
         <v>268</v>
       </c>
@@ -13579,7 +13607,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="7" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" s="2" customFormat="1">
       <c r="A7" s="2" t="s">
         <v>272</v>
       </c>
@@ -13593,7 +13621,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="8" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" s="2" customFormat="1">
       <c r="A8" s="2" t="s">
         <v>277</v>
       </c>
@@ -13607,7 +13635,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="9" spans="1:6" s="2" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" s="2" customFormat="1" ht="16" thickBot="1">
       <c r="A9" s="2" t="s">
         <v>281</v>
       </c>
@@ -13621,7 +13649,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="10" spans="1:6" s="2" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" s="2" customFormat="1" ht="16" thickBot="1">
       <c r="A10" s="2" t="s">
         <v>287</v>
       </c>
@@ -13641,7 +13669,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="11" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" s="2" customFormat="1">
       <c r="A11" s="2" t="s">
         <v>293</v>
       </c>
@@ -13655,7 +13683,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="12" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" s="4" customFormat="1">
       <c r="A12" s="4" t="s">
         <v>297</v>
       </c>
@@ -13669,7 +13697,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="13" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" s="2" customFormat="1">
       <c r="A13" s="2" t="s">
         <v>303</v>
       </c>
@@ -13683,7 +13711,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="14" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" s="2" customFormat="1">
       <c r="A14" s="2" t="s">
         <v>748</v>
       </c>
@@ -13700,7 +13728,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="15" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" s="2" customFormat="1">
       <c r="A15" s="2" t="s">
         <v>870</v>
       </c>
@@ -13717,7 +13745,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="16" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" s="2" customFormat="1">
       <c r="A16" s="2" t="s">
         <v>895</v>
       </c>
@@ -13734,7 +13762,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="17" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" s="2" customFormat="1">
       <c r="A17" s="2" t="s">
         <v>903</v>
       </c>
@@ -13751,7 +13779,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="18" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" s="4" customFormat="1">
       <c r="A18" s="4" t="s">
         <v>907</v>
       </c>
@@ -13765,7 +13793,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="19" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" s="4" customFormat="1">
       <c r="A19" s="4" t="s">
         <v>911</v>
       </c>
@@ -13779,7 +13807,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="20" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" s="2" customFormat="1">
       <c r="A20" s="2" t="s">
         <v>937</v>
       </c>
@@ -13793,7 +13821,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="21" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" s="2" customFormat="1">
       <c r="A21" s="2" t="s">
         <v>946</v>
       </c>
@@ -13807,7 +13835,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="22" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" s="2" customFormat="1">
       <c r="A22" s="2" t="s">
         <v>951</v>
       </c>
@@ -13824,7 +13852,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="23" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" s="2" customFormat="1">
       <c r="A23" s="2" t="s">
         <v>958</v>
       </c>
@@ -13841,7 +13869,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="24" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" s="2" customFormat="1">
       <c r="A24" s="2" t="s">
         <v>964</v>
       </c>
@@ -13858,7 +13886,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="25" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" s="2" customFormat="1">
       <c r="A25" s="2" t="s">
         <v>981</v>
       </c>
@@ -13881,14 +13909,14 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE3F7B10-E9D7-394E-88EE-E3C3786C779E}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -13902,7 +13930,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" s="4" customFormat="1">
       <c r="A2" s="4" t="s">
         <v>175</v>
       </c>
@@ -13916,7 +13944,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" s="4" customFormat="1">
       <c r="A3" s="4" t="s">
         <v>185</v>
       </c>
@@ -13930,7 +13958,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" s="4" customFormat="1">
       <c r="A4" s="4" t="s">
         <v>190</v>
       </c>
@@ -13944,7 +13972,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" s="2" customFormat="1">
       <c r="A5" s="2" t="s">
         <v>845</v>
       </c>
@@ -13958,7 +13986,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" s="2" customFormat="1">
       <c r="A6" s="2" t="s">
         <v>852</v>
       </c>
@@ -13972,7 +14000,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="7" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" s="4" customFormat="1">
       <c r="A7" s="4" t="s">
         <v>916</v>
       </c>
@@ -13994,14 +14022,14 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C2F9903-2165-8846-946B-B401C9D8DB67}">
   <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="36.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="36.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="85.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
@@ -14016,7 +14044,7 @@
       </c>
       <c r="E1" s="2"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="2" t="s">
         <v>670</v>
       </c>
@@ -14039,7 +14067,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="2" t="s">
         <v>681</v>
       </c>
@@ -14056,7 +14084,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="2" t="s">
         <v>689</v>
       </c>
@@ -14081,9 +14109,9 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45DDC3CB-E423-7D48-9BE9-147CF6221632}">
   <dimension ref="B5:C10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:3">
       <c r="B5" s="1" t="s">
         <v>75</v>
       </c>
@@ -14091,7 +14119,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:3">
       <c r="B6" s="1" t="s">
         <v>330</v>
       </c>
@@ -14099,7 +14127,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:3">
       <c r="B7" s="1" t="s">
         <v>771</v>
       </c>
@@ -14107,7 +14135,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:3">
       <c r="B8" s="1" t="s">
         <v>319</v>
       </c>
@@ -14115,7 +14143,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:3">
       <c r="B9" s="1" t="s">
         <v>665</v>
       </c>
@@ -14123,7 +14151,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:3">
       <c r="B10" s="1" t="s">
         <v>1027</v>
       </c>
@@ -14137,7 +14165,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD29CB13-D1F4-2448-8D40-3F8127B9D4DA}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:F140"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="82" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
@@ -14147,7 +14175,7 @@
     <col min="6" max="6" width="36.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" s="2" customFormat="1">
       <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
@@ -14161,7 +14189,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" s="2" customFormat="1" hidden="1">
       <c r="A2" s="2" t="s">
         <v>52</v>
       </c>
@@ -14178,7 +14206,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="3" spans="1:5" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" s="2" customFormat="1" hidden="1">
       <c r="A3" s="2" t="s">
         <v>70</v>
       </c>
@@ -14192,7 +14220,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:5" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" s="4" customFormat="1" hidden="1">
       <c r="A4" s="4" t="s">
         <v>78</v>
       </c>
@@ -14209,7 +14237,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="5" spans="1:5" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" s="2" customFormat="1" hidden="1">
       <c r="A5" s="2" t="s">
         <v>84</v>
       </c>
@@ -14223,7 +14251,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:5" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" s="2" customFormat="1" hidden="1">
       <c r="A6" s="2" t="s">
         <v>88</v>
       </c>
@@ -14237,7 +14265,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:5" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" s="3" customFormat="1" hidden="1">
       <c r="A7" s="3" t="s">
         <v>94</v>
       </c>
@@ -14251,7 +14279,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="8" spans="1:5" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" s="2" customFormat="1" hidden="1">
       <c r="A8" s="2" t="s">
         <v>105</v>
       </c>
@@ -14268,7 +14296,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="9" spans="1:5" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" s="2" customFormat="1" hidden="1">
       <c r="A9" s="2" t="s">
         <v>111</v>
       </c>
@@ -14285,7 +14313,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" hidden="1">
       <c r="A10" t="s">
         <v>119</v>
       </c>
@@ -14299,7 +14327,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="11" spans="1:5" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" s="4" customFormat="1" hidden="1">
       <c r="A11" s="4" t="s">
         <v>127</v>
       </c>
@@ -14316,7 +14344,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="12" spans="1:5" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" s="4" customFormat="1" hidden="1">
       <c r="A12" s="4" t="s">
         <v>127</v>
       </c>
@@ -14333,7 +14361,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="13" spans="1:5" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" s="2" customFormat="1" hidden="1">
       <c r="A13" s="2" t="s">
         <v>137</v>
       </c>
@@ -14347,7 +14375,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="14" spans="1:5" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" s="3" customFormat="1" hidden="1">
       <c r="A14" s="3" t="s">
         <v>94</v>
       </c>
@@ -14361,7 +14389,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="15" spans="1:5" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" s="2" customFormat="1" hidden="1">
       <c r="A15" s="2" t="s">
         <v>137</v>
       </c>
@@ -14378,7 +14406,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="16" spans="1:5" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" s="2" customFormat="1" hidden="1">
       <c r="A16" s="2" t="s">
         <v>149</v>
       </c>
@@ -14395,7 +14423,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="17" spans="1:5" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" s="2" customFormat="1" hidden="1">
       <c r="A17" s="2" t="s">
         <v>155</v>
       </c>
@@ -14412,7 +14440,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="18" spans="1:5" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" s="2" customFormat="1" hidden="1">
       <c r="A18" s="2" t="s">
         <v>111</v>
       </c>
@@ -14429,7 +14457,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" hidden="1">
       <c r="A19" t="s">
         <v>162</v>
       </c>
@@ -14443,7 +14471,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" hidden="1">
       <c r="A20" t="s">
         <v>169</v>
       </c>
@@ -14457,7 +14485,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="21" spans="1:5" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" s="4" customFormat="1" hidden="1">
       <c r="A21" s="4" t="s">
         <v>175</v>
       </c>
@@ -14471,7 +14499,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="22" spans="1:5" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" s="4" customFormat="1" hidden="1">
       <c r="A22" s="4" t="s">
         <v>185</v>
       </c>
@@ -14485,7 +14513,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="23" spans="1:5" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" s="4" customFormat="1" hidden="1">
       <c r="A23" s="4" t="s">
         <v>190</v>
       </c>
@@ -14499,7 +14527,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" hidden="1">
       <c r="A24" t="s">
         <v>199</v>
       </c>
@@ -14513,7 +14541,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" hidden="1">
       <c r="A25" t="s">
         <v>211</v>
       </c>
@@ -14527,7 +14555,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" hidden="1">
       <c r="A26" t="s">
         <v>221</v>
       </c>
@@ -14541,7 +14569,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" hidden="1">
       <c r="A27" t="s">
         <v>233</v>
       </c>
@@ -14555,7 +14583,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="28" spans="1:5" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" s="2" customFormat="1" hidden="1">
       <c r="A28" s="2" t="s">
         <v>244</v>
       </c>
@@ -14569,7 +14597,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="29" spans="1:5" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" s="2" customFormat="1" hidden="1">
       <c r="A29" s="2" t="s">
         <v>253</v>
       </c>
@@ -14583,7 +14611,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="30" spans="1:5" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" s="2" customFormat="1" hidden="1">
       <c r="A30" s="2" t="s">
         <v>259</v>
       </c>
@@ -14597,7 +14625,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="31" spans="1:5" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" s="2" customFormat="1" hidden="1">
       <c r="A31" s="2" t="s">
         <v>263</v>
       </c>
@@ -14611,7 +14639,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="32" spans="1:5" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" s="2" customFormat="1" hidden="1">
       <c r="A32" s="2" t="s">
         <v>268</v>
       </c>
@@ -14625,7 +14653,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="33" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" s="2" customFormat="1" hidden="1">
       <c r="A33" s="2" t="s">
         <v>272</v>
       </c>
@@ -14639,7 +14667,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="34" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4" s="2" customFormat="1" hidden="1">
       <c r="A34" s="2" t="s">
         <v>277</v>
       </c>
@@ -14653,7 +14681,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="35" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" s="2" customFormat="1" hidden="1">
       <c r="A35" s="2" t="s">
         <v>281</v>
       </c>
@@ -14667,7 +14695,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="36" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4" s="2" customFormat="1" hidden="1">
       <c r="A36" s="2" t="s">
         <v>287</v>
       </c>
@@ -14681,7 +14709,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="37" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4" s="2" customFormat="1" hidden="1">
       <c r="A37" s="2" t="s">
         <v>293</v>
       </c>
@@ -14695,7 +14723,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="38" spans="1:4" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" s="4" customFormat="1" hidden="1">
       <c r="A38" s="4" t="s">
         <v>297</v>
       </c>
@@ -14709,7 +14737,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="39" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4" s="2" customFormat="1" hidden="1">
       <c r="A39" s="2" t="s">
         <v>303</v>
       </c>
@@ -14723,7 +14751,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="40" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4" hidden="1">
       <c r="A40" t="s">
         <v>313</v>
       </c>
@@ -14737,7 +14765,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="41" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4" hidden="1">
       <c r="A41" t="s">
         <v>324</v>
       </c>
@@ -14751,7 +14779,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4" hidden="1">
       <c r="A42" t="s">
         <v>333</v>
       </c>
@@ -14765,7 +14793,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="43" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4" s="2" customFormat="1" hidden="1">
       <c r="A43" s="2" t="s">
         <v>339</v>
       </c>
@@ -14779,7 +14807,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="44" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4" hidden="1">
       <c r="A44" t="s">
         <v>350</v>
       </c>
@@ -14793,7 +14821,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="45" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4" hidden="1">
       <c r="A45" t="s">
         <v>360</v>
       </c>
@@ -14807,7 +14835,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="46" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:4" hidden="1">
       <c r="A46" t="s">
         <v>360</v>
       </c>
@@ -14821,7 +14849,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4" hidden="1">
       <c r="A47" t="s">
         <v>360</v>
       </c>
@@ -14835,7 +14863,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="48" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:4" hidden="1">
       <c r="A48" t="s">
         <v>377</v>
       </c>
@@ -14849,7 +14877,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" hidden="1">
       <c r="A49" t="s">
         <v>387</v>
       </c>
@@ -14863,7 +14891,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" hidden="1">
       <c r="A50" t="s">
         <v>399</v>
       </c>
@@ -14877,7 +14905,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" hidden="1">
       <c r="A51" t="s">
         <v>408</v>
       </c>
@@ -14891,7 +14919,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" hidden="1">
       <c r="A52" t="s">
         <v>417</v>
       </c>
@@ -14905,7 +14933,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" hidden="1">
       <c r="A53" t="s">
         <v>427</v>
       </c>
@@ -14919,7 +14947,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5" hidden="1">
       <c r="A54" t="s">
         <v>438</v>
       </c>
@@ -14933,7 +14961,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="55" spans="1:5" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5" s="2" customFormat="1" hidden="1">
       <c r="A55" s="2" t="s">
         <v>450</v>
       </c>
@@ -14950,7 +14978,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="56" spans="1:5" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5" s="2" customFormat="1" hidden="1">
       <c r="A56" s="2" t="s">
         <v>461</v>
       </c>
@@ -14967,7 +14995,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="57" spans="1:5" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5" s="2" customFormat="1" hidden="1">
       <c r="A57" s="2" t="s">
         <v>450</v>
       </c>
@@ -14984,7 +15012,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="58" spans="1:5" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" s="2" customFormat="1" hidden="1">
       <c r="A58" s="2" t="s">
         <v>450</v>
       </c>
@@ -15001,7 +15029,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="59" spans="1:5" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5" s="2" customFormat="1" hidden="1">
       <c r="A59" s="2" t="s">
         <v>450</v>
       </c>
@@ -15018,7 +15046,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="60" spans="1:5" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" s="2" customFormat="1" hidden="1">
       <c r="A60" s="2" t="s">
         <v>450</v>
       </c>
@@ -15035,7 +15063,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="61" spans="1:5" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5" s="4" customFormat="1" hidden="1">
       <c r="A61" s="4" t="s">
         <v>480</v>
       </c>
@@ -15052,7 +15080,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="62" spans="1:5" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5" s="2" customFormat="1" hidden="1">
       <c r="A62" s="2" t="s">
         <v>450</v>
       </c>
@@ -15069,7 +15097,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="63" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" s="2" customFormat="1">
       <c r="A63" s="2" t="s">
         <v>491</v>
       </c>
@@ -15083,7 +15111,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="64" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" s="2" customFormat="1">
       <c r="A64" s="2" t="s">
         <v>502</v>
       </c>
@@ -15100,7 +15128,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="65" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:4" s="2" customFormat="1">
       <c r="A65" s="2" t="s">
         <v>511</v>
       </c>
@@ -15114,7 +15142,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="66" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:4" s="2" customFormat="1" hidden="1">
       <c r="A66" s="2" t="s">
         <v>519</v>
       </c>
@@ -15128,7 +15156,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="67" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:4" s="2" customFormat="1" hidden="1">
       <c r="A67" s="2" t="s">
         <v>529</v>
       </c>
@@ -15142,7 +15170,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="68" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4" s="2" customFormat="1" hidden="1">
       <c r="A68" s="2" t="s">
         <v>533</v>
       </c>
@@ -15156,7 +15184,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="69" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4" s="2" customFormat="1" hidden="1">
       <c r="A69" s="2" t="s">
         <v>537</v>
       </c>
@@ -15170,7 +15198,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="70" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4" s="2" customFormat="1" hidden="1">
       <c r="A70" s="2" t="s">
         <v>541</v>
       </c>
@@ -15184,7 +15212,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="71" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4" s="2" customFormat="1" hidden="1">
       <c r="A71" s="2" t="s">
         <v>545</v>
       </c>
@@ -15198,7 +15226,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="72" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4" s="2" customFormat="1" hidden="1">
       <c r="A72" s="2" t="s">
         <v>549</v>
       </c>
@@ -15212,7 +15240,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="73" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:4" s="2" customFormat="1" hidden="1">
       <c r="A73" s="2" t="s">
         <v>553</v>
       </c>
@@ -15226,7 +15254,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="74" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:4" s="2" customFormat="1" hidden="1">
       <c r="A74" s="2" t="s">
         <v>557</v>
       </c>
@@ -15240,7 +15268,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="75" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:4" s="2" customFormat="1" hidden="1">
       <c r="A75" s="2" t="s">
         <v>561</v>
       </c>
@@ -15254,7 +15282,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="76" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:4" s="2" customFormat="1" hidden="1">
       <c r="A76" s="2" t="s">
         <v>565</v>
       </c>
@@ -15268,7 +15296,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="77" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:4" s="2" customFormat="1" hidden="1">
       <c r="A77" s="2" t="s">
         <v>569</v>
       </c>
@@ -15282,7 +15310,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="78" spans="1:4" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:4" s="8" customFormat="1" hidden="1">
       <c r="A78" s="8" t="s">
         <v>574</v>
       </c>
@@ -15296,7 +15324,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="79" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:4" hidden="1">
       <c r="A79" t="s">
         <v>584</v>
       </c>
@@ -15310,7 +15338,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="80" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:4" hidden="1">
       <c r="A80" t="s">
         <v>593</v>
       </c>
@@ -15324,7 +15352,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:5" hidden="1">
       <c r="A81" t="s">
         <v>601</v>
       </c>
@@ -15338,7 +15366,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="82" spans="1:5" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:5" s="2" customFormat="1" hidden="1">
       <c r="A82" s="2" t="s">
         <v>450</v>
       </c>
@@ -15355,7 +15383,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="83" spans="1:5" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:5" s="2" customFormat="1" hidden="1">
       <c r="A83" s="2" t="s">
         <v>450</v>
       </c>
@@ -15372,7 +15400,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="84" spans="1:5" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:5" s="2" customFormat="1" hidden="1">
       <c r="A84" s="2" t="s">
         <v>621</v>
       </c>
@@ -15386,7 +15414,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:5" hidden="1">
       <c r="A85" t="s">
         <v>628</v>
       </c>
@@ -15400,7 +15428,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:5" hidden="1">
       <c r="A86" t="s">
         <v>638</v>
       </c>
@@ -15414,7 +15442,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="87" spans="1:5" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:5" s="2" customFormat="1" hidden="1">
       <c r="A87" s="2" t="s">
         <v>647</v>
       </c>
@@ -15428,7 +15456,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:5" hidden="1">
       <c r="A88" t="s">
         <v>659</v>
       </c>
@@ -15442,7 +15470,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:5" hidden="1">
       <c r="A89" t="s">
         <v>670</v>
       </c>
@@ -15459,7 +15487,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:5" hidden="1">
       <c r="A90" t="s">
         <v>681</v>
       </c>
@@ -15476,7 +15504,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:5" hidden="1">
       <c r="A91" t="s">
         <v>689</v>
       </c>
@@ -15493,7 +15521,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:5" hidden="1">
       <c r="A92" t="s">
         <v>695</v>
       </c>
@@ -15507,7 +15535,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:5" hidden="1">
       <c r="A93" t="s">
         <v>705</v>
       </c>
@@ -15521,7 +15549,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:5" hidden="1">
       <c r="A94" t="s">
         <v>705</v>
       </c>
@@ -15535,7 +15563,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:5" hidden="1">
       <c r="A95" t="s">
         <v>705</v>
       </c>
@@ -15549,7 +15577,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:5" hidden="1">
       <c r="A96" t="s">
         <v>705</v>
       </c>
@@ -15563,7 +15591,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="97" spans="1:6" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:6" s="4" customFormat="1" hidden="1">
       <c r="A97" s="4" t="s">
         <v>127</v>
       </c>
@@ -15580,7 +15608,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:6" hidden="1">
       <c r="A98" t="s">
         <v>734</v>
       </c>
@@ -15594,7 +15622,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:6" hidden="1">
       <c r="A99" t="s">
         <v>408</v>
       </c>
@@ -15608,7 +15636,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="100" spans="1:6" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:6" s="2" customFormat="1" hidden="1">
       <c r="A100" s="2" t="s">
         <v>748</v>
       </c>
@@ -15622,7 +15650,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="101" spans="1:6" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:6" s="2" customFormat="1" hidden="1">
       <c r="A101" s="2" t="s">
         <v>756</v>
       </c>
@@ -15636,7 +15664,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:6" hidden="1">
       <c r="A102" t="s">
         <v>765</v>
       </c>
@@ -15650,7 +15678,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="103" spans="1:6" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6" s="2" customFormat="1" hidden="1">
       <c r="A103" s="2" t="s">
         <v>774</v>
       </c>
@@ -15670,7 +15698,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="104" spans="1:6" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6" s="2" customFormat="1" hidden="1">
       <c r="A104" s="2" t="s">
         <v>780</v>
       </c>
@@ -15690,7 +15718,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="105" spans="1:6" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:6" s="2" customFormat="1" hidden="1">
       <c r="A105" s="2" t="s">
         <v>784</v>
       </c>
@@ -15710,7 +15738,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6" hidden="1">
       <c r="A106" t="s">
         <v>788</v>
       </c>
@@ -15724,7 +15752,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="107" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6" hidden="1">
       <c r="A107" t="s">
         <v>796</v>
       </c>
@@ -15738,7 +15766,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="108" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:6" hidden="1">
       <c r="A108" t="s">
         <v>801</v>
       </c>
@@ -15752,7 +15780,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="109" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:6" hidden="1">
       <c r="A109" t="s">
         <v>808</v>
       </c>
@@ -15766,7 +15794,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="110" spans="1:6" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:6" s="2" customFormat="1" hidden="1">
       <c r="A110" s="2" t="s">
         <v>814</v>
       </c>
@@ -15786,7 +15814,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="111" spans="1:6" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:6" s="2" customFormat="1" hidden="1">
       <c r="A111" s="2" t="s">
         <v>822</v>
       </c>
@@ -15806,7 +15834,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="112" spans="1:6" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:6" s="2" customFormat="1" hidden="1">
       <c r="A112" s="2" t="s">
         <v>828</v>
       </c>
@@ -15826,7 +15854,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="113" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:4" hidden="1">
       <c r="A113" t="s">
         <v>833</v>
       </c>
@@ -15840,7 +15868,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="114" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:4" hidden="1">
       <c r="A114" t="s">
         <v>705</v>
       </c>
@@ -15854,7 +15882,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="115" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:4" s="2" customFormat="1" hidden="1">
       <c r="A115" s="2" t="s">
         <v>845</v>
       </c>
@@ -15868,7 +15896,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="116" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:4" s="2" customFormat="1" hidden="1">
       <c r="A116" s="2" t="s">
         <v>852</v>
       </c>
@@ -15882,7 +15910,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="117" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:4" hidden="1">
       <c r="A117" t="s">
         <v>859</v>
       </c>
@@ -15896,7 +15924,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="118" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:4" s="2" customFormat="1" hidden="1">
       <c r="A118" s="2" t="s">
         <v>870</v>
       </c>
@@ -15910,7 +15938,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="119" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:4" hidden="1">
       <c r="A119" t="s">
         <v>875</v>
       </c>
@@ -15924,7 +15952,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="120" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:4" s="2" customFormat="1" hidden="1">
       <c r="A120" s="2" t="s">
         <v>882</v>
       </c>
@@ -15938,7 +15966,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="121" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:4" hidden="1">
       <c r="A121" t="s">
         <v>695</v>
       </c>
@@ -15952,7 +15980,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="122" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:4" s="2" customFormat="1" hidden="1">
       <c r="A122" s="2" t="s">
         <v>895</v>
       </c>
@@ -15966,7 +15994,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="123" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:4" s="2" customFormat="1" hidden="1">
       <c r="A123" s="2" t="s">
         <v>903</v>
       </c>
@@ -15980,7 +16008,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="124" spans="1:4" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:4" s="4" customFormat="1" hidden="1">
       <c r="A124" s="4" t="s">
         <v>907</v>
       </c>
@@ -15994,7 +16022,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="125" spans="1:4" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:4" s="4" customFormat="1" hidden="1">
       <c r="A125" s="4" t="s">
         <v>911</v>
       </c>
@@ -16008,7 +16036,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="126" spans="1:4" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:4" s="4" customFormat="1" hidden="1">
       <c r="A126" s="4" t="s">
         <v>916</v>
       </c>
@@ -16022,7 +16050,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="127" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:4" s="2" customFormat="1" hidden="1">
       <c r="A127" s="2" t="s">
         <v>924</v>
       </c>
@@ -16036,7 +16064,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="128" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:4" s="2" customFormat="1" hidden="1">
       <c r="A128" s="2" t="s">
         <v>929</v>
       </c>
@@ -16050,7 +16078,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="129" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:4" s="2" customFormat="1" hidden="1">
       <c r="A129" s="2" t="s">
         <v>933</v>
       </c>
@@ -16064,7 +16092,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="130" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:4" s="2" customFormat="1" hidden="1">
       <c r="A130" s="2" t="s">
         <v>937</v>
       </c>
@@ -16078,7 +16106,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="131" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:4" s="2" customFormat="1" hidden="1">
       <c r="A131" s="2" t="s">
         <v>946</v>
       </c>
@@ -16092,7 +16120,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="132" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:4" s="2" customFormat="1" hidden="1">
       <c r="A132" s="2" t="s">
         <v>951</v>
       </c>
@@ -16106,7 +16134,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="133" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:4" s="2" customFormat="1" hidden="1">
       <c r="A133" s="2" t="s">
         <v>958</v>
       </c>
@@ -16120,7 +16148,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="134" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:4" s="2" customFormat="1" hidden="1">
       <c r="A134" s="2" t="s">
         <v>964</v>
       </c>
@@ -16134,7 +16162,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="135" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:4" s="2" customFormat="1" hidden="1">
       <c r="A135" s="2" t="s">
         <v>155</v>
       </c>
@@ -16148,7 +16176,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="136" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:4" hidden="1">
       <c r="A136" t="s">
         <v>765</v>
       </c>
@@ -16162,7 +16190,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="137" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:4" s="2" customFormat="1" hidden="1">
       <c r="A137" s="2" t="s">
         <v>981</v>
       </c>
@@ -16176,7 +16204,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="138" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:4" hidden="1">
       <c r="A138" t="s">
         <v>988</v>
       </c>
@@ -16190,7 +16218,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="139" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:4" hidden="1">
       <c r="A139" t="s">
         <v>734</v>
       </c>
@@ -16204,7 +16232,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="140" spans="1:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:4" s="2" customFormat="1" hidden="1">
       <c r="A140" s="2" t="s">
         <v>84</v>
       </c>
@@ -16236,17 +16264,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{916CD87E-FB8F-5F4E-9AB4-0BF93ECEEA89}">
-  <dimension ref="A1:F31"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F30"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.33203125" customWidth="1"/>
-    <col min="2" max="2" width="20.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="58.83203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="62.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
         <v>771</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -16256,46 +16284,55 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="13" t="s">
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
         <v>330</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1022</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="16" t="s">
+    <row r="3" spans="1:6" s="14" customFormat="1">
+      <c r="A3" s="14" t="s">
         <v>676</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="14" t="s">
         <v>1050</v>
       </c>
-      <c r="F3" s="17" t="s">
-        <v>1072</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="13" t="s">
+      <c r="F3" s="14" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
         <v>319</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>1023</v>
       </c>
       <c r="F4" t="s">
-        <v>1069</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="14" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" s="15" customFormat="1" ht="16">
+      <c r="A5" s="15" t="s">
         <v>356</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>1065</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="13" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>1072</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
         <v>206</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -16305,159 +16342,166 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="7" spans="1:6" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="16" t="s">
+    <row r="7" spans="1:6" s="14" customFormat="1">
+      <c r="A7" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="14" t="s">
         <v>1051</v>
       </c>
     </row>
-    <row r="8" spans="1:6" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="16" t="s">
+    <row r="8" spans="1:6" s="14" customFormat="1">
+      <c r="A8" s="14" t="s">
         <v>382</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="14" t="s">
         <v>1060</v>
       </c>
     </row>
-    <row r="9" spans="1:6" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="16" t="s">
+    <row r="9" spans="1:6" s="14" customFormat="1">
+      <c r="A9" s="14" t="s">
         <v>239</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="14" t="s">
         <v>1051</v>
       </c>
     </row>
-    <row r="10" spans="1:6" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="16" t="s">
+    <row r="10" spans="1:6" s="14" customFormat="1">
+      <c r="A10" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="14" t="s">
         <v>1022</v>
       </c>
     </row>
-    <row r="11" spans="1:6" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="16" t="s">
+    <row r="11" spans="1:6" s="14" customFormat="1">
+      <c r="A11" s="14" t="s">
         <v>250</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="14" t="s">
         <v>1052</v>
       </c>
     </row>
-    <row r="12" spans="1:6" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="16" t="s">
+    <row r="12" spans="1:6" s="14" customFormat="1">
+      <c r="A12" s="14" t="s">
         <v>607</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="14" t="s">
         <v>1053</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="13" t="s">
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
         <v>422</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>1058</v>
       </c>
       <c r="E13" t="s">
-        <v>1071</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="16" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" s="14" customFormat="1">
+      <c r="A14" s="14" t="s">
         <v>365</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="14" t="s">
         <v>1051</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="13" t="s">
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
         <v>665</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>1022</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="13" t="s">
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
         <v>181</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>1022</v>
       </c>
     </row>
-    <row r="17" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="16" t="s">
+    <row r="17" spans="1:6" s="14" customFormat="1">
+      <c r="A17" s="14" t="s">
         <v>444</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="14" t="s">
         <v>1060</v>
       </c>
     </row>
-    <row r="18" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="16" t="s">
+    <row r="18" spans="1:6" s="14" customFormat="1">
+      <c r="A18" s="14" t="s">
         <v>433</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="14" t="s">
         <v>1060</v>
       </c>
     </row>
-    <row r="19" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="14" t="s">
+    <row r="19" spans="1:6" s="13" customFormat="1" ht="20">
+      <c r="A19" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="13" t="s">
         <v>1054</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="13" t="s">
         <v>1054</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="16" t="s">
+      <c r="F19" s="17"/>
+    </row>
+    <row r="20" spans="1:6" s="14" customFormat="1" ht="20">
+      <c r="A20" s="14" t="s">
         <v>404</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="14" t="s">
         <v>1050</v>
       </c>
-      <c r="D20" s="17" t="s">
-        <v>1064</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" s="13" t="s">
+      <c r="D20" s="14" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>1075</v>
+      </c>
+      <c r="F20" s="18" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" t="s">
         <v>393</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>1061</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>1062</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="16" t="s">
+    </row>
+    <row r="22" spans="1:6" s="14" customFormat="1">
+      <c r="A22" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="14" t="s">
         <v>1051</v>
       </c>
     </row>
-    <row r="23" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="16" t="s">
+    <row r="23" spans="1:6" s="14" customFormat="1">
+      <c r="A23" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="14" t="s">
         <v>1051</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" s="13" t="s">
+    <row r="24" spans="1:6">
+      <c r="A24" t="s">
         <v>456</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -16467,30 +16511,30 @@
         <v>1059</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="E24" t="s">
-        <v>1068</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" s="13" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" t="s">
         <v>497</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>1022</v>
       </c>
     </row>
-    <row r="26" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="16" t="s">
+    <row r="26" spans="1:6" s="14" customFormat="1">
+      <c r="A26" s="14" t="s">
         <v>865</v>
       </c>
-      <c r="B26" s="17" t="s">
-        <v>1063</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27" s="13" t="s">
+      <c r="B26" s="14" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" t="s">
         <v>654</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -16500,11 +16544,11 @@
         <v>1058</v>
       </c>
       <c r="E27" t="s">
-        <v>1066</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A28" s="13" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" t="s">
         <v>345</v>
       </c>
       <c r="B28" s="1" t="s">
@@ -16514,24 +16558,21 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="29" spans="1:5" s="19" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="18" t="s">
+    <row r="29" spans="1:6" s="15" customFormat="1">
+      <c r="A29" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="B29" s="19" t="s">
+      <c r="B29" s="15" t="s">
         <v>1056</v>
       </c>
     </row>
-    <row r="30" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="16" t="s">
+    <row r="30" spans="1:6" s="14" customFormat="1">
+      <c r="A30" s="14" t="s">
         <v>525</v>
       </c>
-      <c r="B30" s="17" t="s">
+      <c r="B30" s="14" t="s">
         <v>1051</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A31" s="13"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:A1048467">
@@ -16544,7 +16585,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6C22C05-6386-4B49-853E-B77F21E46829}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="52.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="52.1640625" bestFit="1" customWidth="1"/>
@@ -16552,7 +16593,7 @@
     <col min="5" max="5" width="99.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -16566,7 +16607,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" s="2" customFormat="1">
       <c r="A2" s="2" t="s">
         <v>601</v>
       </c>
@@ -16583,7 +16624,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" s="2" customFormat="1">
       <c r="A3" s="2" t="s">
         <v>788</v>
       </c>
@@ -16600,7 +16641,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" s="2" customFormat="1">
       <c r="A4" s="2" t="s">
         <v>796</v>
       </c>
@@ -16617,7 +16658,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="5" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" s="4" customFormat="1">
       <c r="A5" s="4" t="s">
         <v>801</v>
       </c>
@@ -16634,7 +16675,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" s="2" customFormat="1">
       <c r="A6" s="2" t="s">
         <v>808</v>
       </c>
@@ -16651,7 +16692,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" s="2" customFormat="1">
       <c r="A7" s="2" t="s">
         <v>833</v>
       </c>
@@ -16676,12 +16717,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F2D37CA-29C3-BD49-9326-06CF486A4EFB}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="5" max="5" width="57.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" s="4" customFormat="1">
       <c r="A1" s="4" t="s">
         <v>417</v>
       </c>
@@ -16701,7 +16742,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" s="8" customFormat="1">
       <c r="A2" s="8" t="s">
         <v>574</v>
       </c>
@@ -16723,12 +16764,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B4857D5-237B-E945-A0DB-32FAF0CE7CD3}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="18.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -16742,7 +16783,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" s="8" customFormat="1">
       <c r="A2" s="2" t="s">
         <v>119</v>
       </c>
@@ -16756,7 +16797,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" s="8" customFormat="1">
       <c r="A3" s="2" t="s">
         <v>162</v>
       </c>
@@ -16770,7 +16811,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" s="8" customFormat="1">
       <c r="A4" s="2" t="s">
         <v>169</v>
       </c>
@@ -16784,7 +16825,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
         <v>233</v>
       </c>
@@ -16798,7 +16839,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
         <v>584</v>
       </c>
@@ -16812,7 +16853,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
         <v>593</v>
       </c>
@@ -16826,7 +16867,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
         <v>360</v>
       </c>
@@ -16840,7 +16881,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
         <v>360</v>
       </c>
@@ -16854,7 +16895,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
         <v>360</v>
       </c>
@@ -16876,19 +16917,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA47AA37-095C-2D41-ADC5-D8C2D0281F2E}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
         <v>433</v>
       </c>
@@ -16901,14 +16942,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C270AD3-01ED-274B-829E-C282786A8465}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="36" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35.1640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="35.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" s="2" customFormat="1">
       <c r="A1" s="2" t="s">
         <v>199</v>
       </c>
@@ -16928,7 +16969,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" s="3" customFormat="1">
       <c r="A2" s="3" t="s">
         <v>211</v>
       </c>
@@ -16950,7 +16991,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7511E3A-EAFE-814F-AE01-B1ED38B5D125}">
   <dimension ref="A1:E15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="44.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
@@ -16959,7 +17000,7 @@
     <col min="5" max="5" width="35.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -16973,7 +17014,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" s="3" customFormat="1">
       <c r="A2" s="3" t="s">
         <v>387</v>
       </c>
@@ -16987,7 +17028,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" s="2" customFormat="1">
       <c r="A3" s="2" t="s">
         <v>408</v>
       </c>
@@ -17004,7 +17045,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" s="2" customFormat="1">
       <c r="A4" s="2" t="s">
         <v>628</v>
       </c>
@@ -17018,7 +17059,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" s="2" customFormat="1">
       <c r="A5" s="2" t="s">
         <v>638</v>
       </c>
@@ -17032,7 +17073,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" s="2" customFormat="1">
       <c r="A6" s="2" t="s">
         <v>695</v>
       </c>
@@ -17046,7 +17087,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" s="2" customFormat="1">
       <c r="A7" s="2" t="s">
         <v>705</v>
       </c>
@@ -17060,7 +17101,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" s="2" customFormat="1">
       <c r="A8" s="2" t="s">
         <v>705</v>
       </c>
@@ -17074,7 +17115,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" s="2" customFormat="1">
       <c r="A9" s="2" t="s">
         <v>705</v>
       </c>
@@ -17088,7 +17129,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" s="2" customFormat="1">
       <c r="A10" s="2" t="s">
         <v>705</v>
       </c>
@@ -17102,7 +17143,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" s="2" customFormat="1">
       <c r="A11" s="2" t="s">
         <v>734</v>
       </c>
@@ -17116,7 +17157,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="12" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" s="2" customFormat="1">
       <c r="A12" s="2" t="s">
         <v>408</v>
       </c>
@@ -17130,7 +17171,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="13" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" s="2" customFormat="1">
       <c r="A13" s="2" t="s">
         <v>705</v>
       </c>
@@ -17144,7 +17185,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="14" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" s="2" customFormat="1">
       <c r="A14" s="2" t="s">
         <v>695</v>
       </c>
@@ -17158,7 +17199,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="15" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" s="2" customFormat="1">
       <c r="A15" s="2" t="s">
         <v>734</v>
       </c>

--- a/MORITZ APA 136.xlsx
+++ b/MORITZ APA 136.xlsx
@@ -8,36 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/moriheidtmann/Documents/Work/Playwrite_VS_Extention/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9F69131-C58E-594C-A453-4C81EAD3FC11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF3ECAC7-2C29-0540-B157-8FA115D4A959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
-    <sheet name="SORTED" sheetId="2" r:id="rId2"/>
-    <sheet name="OVERWIEW" sheetId="15" r:id="rId3"/>
-    <sheet name="GREECE" sheetId="13" r:id="rId4"/>
-    <sheet name="HUNGARY" sheetId="11" r:id="rId5"/>
-    <sheet name="Nordic" sheetId="10" r:id="rId6"/>
-    <sheet name="BALTIC" sheetId="12" r:id="rId7"/>
-    <sheet name="CZECH REPUBLIC" sheetId="9" r:id="rId8"/>
-    <sheet name="NETHERLANDS" sheetId="6" r:id="rId9"/>
-    <sheet name="FRANCE" sheetId="5" r:id="rId10"/>
-    <sheet name="GERMANY" sheetId="3" r:id="rId11"/>
-    <sheet name="ITALY" sheetId="4" r:id="rId12"/>
-    <sheet name="BULGARIA" sheetId="8" r:id="rId13"/>
-    <sheet name="INFO" sheetId="7" r:id="rId14"/>
+    <sheet name="OVERWIEW" sheetId="15" r:id="rId1"/>
+    <sheet name="Worksheet" sheetId="1" r:id="rId2"/>
+    <sheet name="SORTED" sheetId="2" r:id="rId3"/>
+    <sheet name="GERMANY" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">GERMANY!$A$1:$A$1048461</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">SORTED!$D$1:$D$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">GERMANY!$A$1:$A$1048461</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">SORTED!$D$1:$D$140</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3861" uniqueCount="1077">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3632" uniqueCount="1069">
   <si>
     <t>ae_authorisationNotificationDateStr</t>
   </si>
@@ -3096,15 +3086,6 @@
     <t>Deutsche Börse AG manages the relationship with the client with respect to MiFIR Data Products for the Deutsche Börse Group trading venues, such as EEX, Eurex, and XETRA simplifying access. </t>
   </si>
   <si>
-    <t>https://www.ice.com/futures-europe/mifidii</t>
-  </si>
-  <si>
-    <t>commodities</t>
-  </si>
-  <si>
-    <t>infrastructure</t>
-  </si>
-  <si>
     <t>EURONEXT</t>
   </si>
   <si>
@@ -3114,30 +3095,6 @@
     <t>https://www.bse-sofia.bg/en/apa-trading-data</t>
   </si>
   <si>
-    <t>DONE</t>
-  </si>
-  <si>
-    <t>https://prices.wienerborse.at/#tab-content1</t>
-  </si>
-  <si>
-    <t>LUXEMBURG</t>
-  </si>
-  <si>
-    <t>https://www.athexgroup.gr/en/market-data/data-services/delayed-feed#:~:text=Pre,Access%20the%20related%20files%20here</t>
-  </si>
-  <si>
-    <t>Daten über XATH/XADE</t>
-  </si>
-  <si>
-    <t>https://www.enexgroup.gr/post-trade#:~:text=Post%20Trade%20Transparency%20for%20HENEX,midnight%20of%20the%20next%20business%C2%A0day</t>
-  </si>
-  <si>
-    <t>Daten über HENEX-Portal</t>
-  </si>
-  <si>
-    <t>https://www.bankofgreece.gr/en/main-tasks/markets/hdat/pre-trade-data#:~:text=HDAT%20makes%20pre,600%2F2014%20%28MIFIR</t>
-  </si>
-  <si>
     <t>NASDAQ</t>
   </si>
   <si>
@@ -3180,15 +3137,6 @@
     <t>https://www.mds.deutsche-boerse.com/mds-en/real-time-data/mifid-ii-disaggregated-information-products</t>
   </si>
   <si>
-    <t>alternative</t>
-  </si>
-  <si>
-    <t>https://www.bet.hu/site/Angol/pages/derivatives-market#:~:text=Magyar</t>
-  </si>
-  <si>
-    <t>https://bet.hu/site/Angol/Contents/Prices-and-Markets/Data-download#:~:text=Share%20section%3A%20Download</t>
-  </si>
-  <si>
     <t>Deutsche Börse Group</t>
   </si>
   <si>
@@ -3222,9 +3170,6 @@
     <t>NASDAQ Baltic</t>
   </si>
   <si>
-    <t>ICE is for startups i dont think they have a personal data vendor</t>
-  </si>
-  <si>
     <t>Bucharest</t>
   </si>
   <si>
@@ -3267,7 +3212,28 @@
     <t>https://www.borzamalta.com.mt/trading</t>
   </si>
   <si>
-    <t>CBOE &amp; Euronext&amp; ICE&amp; CME</t>
+    <t>ICE POST</t>
+  </si>
+  <si>
+    <t>https://www.ice.com/report/61</t>
+  </si>
+  <si>
+    <t>https://www.ice.com/report/60</t>
+  </si>
+  <si>
+    <t>CME</t>
+  </si>
+  <si>
+    <t>https://www.traxapa.com/apa-publication/#/trades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBOE &amp; Euronext </t>
+  </si>
+  <si>
+    <t>ICE PRE</t>
+  </si>
+  <si>
+    <t>NOT IN THE EU</t>
   </si>
 </sst>
 </file>
@@ -3335,7 +3301,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3366,14 +3332,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -3396,21 +3356,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -3426,7 +3371,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -3436,6 +3380,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -3740,6 +3685,368 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{916CD87E-FB8F-5F4E-9AB4-0BF93ECEEA89}">
+  <dimension ref="A1:F33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="15.33203125" customWidth="1"/>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="58.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="62.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>771</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="13" customFormat="1">
+      <c r="A3" s="13" t="s">
+        <v>676</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>1036</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>319</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="F4" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" s="14" customFormat="1" ht="16">
+      <c r="A5" s="14" t="s">
+        <v>356</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>1048</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>1057</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>206</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="13" customFormat="1">
+      <c r="A7" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="13" customFormat="1">
+      <c r="A8" s="13" t="s">
+        <v>382</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="13" customFormat="1">
+      <c r="A9" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" s="13" customFormat="1">
+      <c r="A10" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" s="13" customFormat="1">
+      <c r="A11" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" s="13" customFormat="1">
+      <c r="A12" s="13" t="s">
+        <v>607</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>422</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E13" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" s="13" customFormat="1">
+      <c r="A14" s="13" t="s">
+        <v>365</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
+        <v>665</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
+        <v>181</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" s="13" customFormat="1">
+      <c r="A17" s="13" t="s">
+        <v>444</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" s="13" customFormat="1">
+      <c r="A18" s="13" t="s">
+        <v>433</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" s="12" customFormat="1" ht="20">
+      <c r="A19" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>1040</v>
+      </c>
+      <c r="F19" s="16"/>
+    </row>
+    <row r="20" spans="1:6" s="13" customFormat="1" ht="20">
+      <c r="A20" s="13" t="s">
+        <v>404</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>1048</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>1060</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" s="13" customFormat="1">
+      <c r="A21" s="13" t="s">
+        <v>393</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" s="13" customFormat="1">
+      <c r="A22" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" s="13" customFormat="1">
+      <c r="A23" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" t="s">
+        <v>456</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>1050</v>
+      </c>
+      <c r="E24" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" t="s">
+        <v>497</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" s="13" customFormat="1">
+      <c r="A26" s="13" t="s">
+        <v>865</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" t="s">
+        <v>654</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E27" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" t="s">
+        <v>345</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" s="14" customFormat="1">
+      <c r="A29" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" s="13" customFormat="1">
+      <c r="A30" s="13" t="s">
+        <v>525</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D31" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D32" s="18" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D33" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:A1048467">
+    <sortCondition ref="A1:A1048467"/>
+  </sortState>
+  <hyperlinks>
+    <hyperlink ref="D32" r:id="rId1" xr:uid="{3D582A70-B0E5-A44F-89C8-C437C8ADF110}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AX140"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
@@ -13412,756 +13719,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41B1068A-70D8-5141-B56A-F887E4222AFE}">
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1">
-      <c r="A1" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>1022</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>1021</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" s="2" customFormat="1">
-      <c r="A2" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" s="2" customFormat="1">
-      <c r="A3" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>1022</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>1020</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" s="2" customFormat="1">
-      <c r="A4" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>1006</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{190D282D-A498-5040-B7ED-BB0A4708E39A}">
-  <dimension ref="A1:F25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="81.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="77.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="143.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="255.83203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>1013</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>1011</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" s="2" customFormat="1">
-      <c r="A2" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>1014</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" s="2" customFormat="1">
-      <c r="A3" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" s="2" customFormat="1">
-      <c r="A4" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" s="2" customFormat="1">
-      <c r="A5" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" s="2" customFormat="1">
-      <c r="A6" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" s="2" customFormat="1">
-      <c r="A7" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" s="2" customFormat="1">
-      <c r="A8" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" s="2" customFormat="1" ht="16" thickBot="1">
-      <c r="A9" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" s="2" customFormat="1" ht="16" thickBot="1">
-      <c r="A10" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>1010</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" s="2" customFormat="1">
-      <c r="A11" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" s="4" customFormat="1">
-      <c r="A12" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" s="2" customFormat="1">
-      <c r="A13" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" s="2" customFormat="1">
-      <c r="A14" s="2" t="s">
-        <v>748</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>749</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>748</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>1018</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" s="2" customFormat="1">
-      <c r="A15" s="2" t="s">
-        <v>870</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>871</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>870</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>1017</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" s="2" customFormat="1">
-      <c r="A16" s="2" t="s">
-        <v>895</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>896</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>895</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" s="2" customFormat="1">
-      <c r="A17" s="2" t="s">
-        <v>903</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>904</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>903</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" s="4" customFormat="1">
-      <c r="A18" s="4" t="s">
-        <v>907</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>908</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>907</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" s="4" customFormat="1">
-      <c r="A19" s="4" t="s">
-        <v>911</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>912</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>911</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" s="2" customFormat="1">
-      <c r="A20" s="2" t="s">
-        <v>937</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>938</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>937</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" s="2" customFormat="1">
-      <c r="A21" s="2" t="s">
-        <v>946</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>947</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>946</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" s="2" customFormat="1">
-      <c r="A22" s="2" t="s">
-        <v>951</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>952</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>951</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" s="2" customFormat="1">
-      <c r="A23" s="2" t="s">
-        <v>958</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>959</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>958</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" s="2" customFormat="1">
-      <c r="A24" s="2" t="s">
-        <v>964</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>965</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>964</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" s="2" customFormat="1">
-      <c r="A25" s="2" t="s">
-        <v>981</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>982</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>981</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:A1048461" xr:uid="{190D282D-A498-5040-B7ED-BB0A4708E39A}"/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE3F7B10-E9D7-394E-88EE-E3C3786C779E}">
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" s="4" customFormat="1">
-      <c r="A2" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" s="4" customFormat="1">
-      <c r="A3" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" s="4" customFormat="1">
-      <c r="A4" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" s="2" customFormat="1">
-      <c r="A5" s="2" t="s">
-        <v>845</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>846</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>845</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" s="2" customFormat="1">
-      <c r="A6" s="2" t="s">
-        <v>852</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>853</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>852</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" s="4" customFormat="1">
-      <c r="A7" s="4" t="s">
-        <v>916</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>917</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>916</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>181</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C2F9903-2165-8846-946B-B401C9D8DB67}">
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="36.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="36.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="85.1640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="2"/>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>671</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>1024</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>1046</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>1047</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="2" t="s">
-        <v>681</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>682</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>681</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>1024</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="2" t="s">
-        <v>689</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>690</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>689</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>1024</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45DDC3CB-E423-7D48-9BE9-147CF6221632}">
-  <dimension ref="B5:C10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="5" spans="2:3">
-      <c r="B5" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3">
-      <c r="B6" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3">
-      <c r="B7" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>1023</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3">
-      <c r="B8" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>1025</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3">
-      <c r="B9" s="1" t="s">
-        <v>665</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3">
-      <c r="B10" s="1" t="s">
-        <v>1027</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD29CB13-D1F4-2448-8D40-3F8127B9D4DA}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:F140"/>
@@ -14203,7 +13761,7 @@
         <v>60</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>1033</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" hidden="1">
@@ -14234,7 +13792,7 @@
         <v>60</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>1039</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" hidden="1">
@@ -14269,7 +13827,7 @@
       <c r="A7" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="11" t="s">
         <v>95</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -14293,7 +13851,7 @@
         <v>101</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1042</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" hidden="1">
@@ -14310,7 +13868,7 @@
         <v>101</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1043</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="10" spans="1:5" hidden="1">
@@ -14341,7 +13899,7 @@
         <v>101</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>1044</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="4" customFormat="1" hidden="1">
@@ -14358,7 +13916,7 @@
         <v>101</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>1044</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="13" spans="1:5" s="2" customFormat="1" hidden="1">
@@ -14403,7 +13961,7 @@
         <v>101</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>1043</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="16" spans="1:5" s="2" customFormat="1" hidden="1">
@@ -14420,7 +13978,7 @@
         <v>101</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>1043</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="2" customFormat="1" hidden="1">
@@ -14437,7 +13995,7 @@
         <v>101</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>1043</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="2" customFormat="1" hidden="1">
@@ -14454,7 +14012,7 @@
         <v>101</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>1043</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="19" spans="1:5" hidden="1">
@@ -14975,7 +14533,7 @@
         <v>456</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>1040</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="56" spans="1:5" s="2" customFormat="1" hidden="1">
@@ -14992,7 +14550,7 @@
         <v>456</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>1046</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="57" spans="1:5" s="2" customFormat="1" hidden="1">
@@ -15076,8 +14634,8 @@
       <c r="D61" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="E61" s="11" t="s">
-        <v>1041</v>
+      <c r="E61" s="10" t="s">
+        <v>1030</v>
       </c>
     </row>
     <row r="62" spans="1:5" s="2" customFormat="1" hidden="1">
@@ -15125,7 +14683,7 @@
         <v>497</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>1045</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="65" spans="1:4" s="2" customFormat="1">
@@ -15484,7 +15042,7 @@
         <v>676</v>
       </c>
       <c r="E89" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="90" spans="1:5" hidden="1">
@@ -15501,7 +15059,7 @@
         <v>676</v>
       </c>
       <c r="E90" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="91" spans="1:5" hidden="1">
@@ -15518,7 +15076,7 @@
         <v>676</v>
       </c>
       <c r="E91" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="92" spans="1:5" hidden="1">
@@ -15605,7 +15163,7 @@
         <v>101</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>1044</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="98" spans="1:6" hidden="1">
@@ -15692,10 +15250,10 @@
         <v>60</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>1034</v>
+        <v>1023</v>
       </c>
       <c r="F103" s="6" t="s">
-        <v>1035</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="104" spans="1:6" s="2" customFormat="1" hidden="1">
@@ -15711,11 +15269,11 @@
       <c r="D104" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E104" s="10" t="s">
-        <v>1034</v>
+      <c r="E104" s="9" t="s">
+        <v>1023</v>
       </c>
       <c r="F104" s="6" t="s">
-        <v>1035</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="105" spans="1:6" s="2" customFormat="1" hidden="1">
@@ -15732,10 +15290,10 @@
         <v>60</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>1034</v>
+        <v>1023</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>1035</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="106" spans="1:6" hidden="1">
@@ -15808,10 +15366,10 @@
         <v>60</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>1036</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="111" spans="1:6" s="2" customFormat="1" hidden="1">
@@ -15828,10 +15386,10 @@
         <v>60</v>
       </c>
       <c r="E111" s="6" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="F111" s="6" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="112" spans="1:6" s="2" customFormat="1" hidden="1">
@@ -15848,10 +15406,10 @@
         <v>60</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="F112" s="6" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="113" spans="1:4" hidden="1">
@@ -16262,339 +15820,20 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{916CD87E-FB8F-5F4E-9AB4-0BF93ECEEA89}">
-  <dimension ref="A1:F30"/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{190D282D-A498-5040-B7ED-BB0A4708E39A}">
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.33203125" customWidth="1"/>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="58.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="62.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="81.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="77.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="143.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="255.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>771</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1023</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1058</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
-        <v>330</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" s="14" customFormat="1">
-      <c r="A3" s="14" t="s">
-        <v>676</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>1050</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
-        <v>319</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>1023</v>
-      </c>
-      <c r="F4" t="s">
-        <v>1067</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" s="15" customFormat="1" ht="16">
-      <c r="A5" s="15" t="s">
-        <v>356</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>1073</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>1063</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>1072</v>
-      </c>
-      <c r="F5" s="16" t="s">
-        <v>1071</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
-        <v>206</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>1023</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>1058</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" s="14" customFormat="1">
-      <c r="A7" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>1051</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" s="14" customFormat="1">
-      <c r="A8" s="14" t="s">
-        <v>382</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" s="14" customFormat="1">
-      <c r="A9" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>1051</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" s="14" customFormat="1">
-      <c r="A10" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" s="14" customFormat="1">
-      <c r="A11" s="14" t="s">
-        <v>250</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>1052</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" s="14" customFormat="1">
-      <c r="A12" s="14" t="s">
-        <v>607</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>1053</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" t="s">
-        <v>422</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>1068</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>1058</v>
-      </c>
-      <c r="E13" t="s">
-        <v>1069</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" s="14" customFormat="1">
-      <c r="A14" s="14" t="s">
-        <v>365</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>1051</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" t="s">
-        <v>665</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" t="s">
-        <v>181</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" s="14" customFormat="1">
-      <c r="A17" s="14" t="s">
-        <v>444</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" s="14" customFormat="1">
-      <c r="A18" s="14" t="s">
-        <v>433</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" s="13" customFormat="1" ht="20">
-      <c r="A19" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>1054</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>1054</v>
-      </c>
-      <c r="F19" s="17"/>
-    </row>
-    <row r="20" spans="1:6" s="14" customFormat="1" ht="20">
-      <c r="A20" s="14" t="s">
-        <v>404</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>1050</v>
-      </c>
-      <c r="D20" s="14" t="s">
-        <v>1063</v>
-      </c>
-      <c r="E20" s="14" t="s">
-        <v>1075</v>
-      </c>
-      <c r="F20" s="18" t="s">
-        <v>1074</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" t="s">
-        <v>393</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>1076</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>1061</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" s="14" customFormat="1">
-      <c r="A22" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>1051</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" s="14" customFormat="1">
-      <c r="A23" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="B23" s="14" t="s">
-        <v>1051</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" t="s">
-        <v>456</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>1055</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>1059</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>1065</v>
-      </c>
-      <c r="E24" t="s">
-        <v>1066</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" t="s">
-        <v>497</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" s="14" customFormat="1">
-      <c r="A26" s="14" t="s">
-        <v>865</v>
-      </c>
-      <c r="B26" s="14" t="s">
-        <v>1062</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" t="s">
-        <v>654</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>1057</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>1058</v>
-      </c>
-      <c r="E27" t="s">
-        <v>1064</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" t="s">
-        <v>345</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>1023</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>1058</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" s="15" customFormat="1">
-      <c r="A29" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="B29" s="15" t="s">
-        <v>1056</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" s="14" customFormat="1">
-      <c r="A30" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="B30" s="14" t="s">
-        <v>1051</v>
-      </c>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:A1048467">
-    <sortCondition ref="A1:A1048467"/>
-  </sortState>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6C22C05-6386-4B49-853E-B77F21E46829}">
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="52.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="52.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="99.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
         <v>6</v>
       </c>
       <c r="B1" t="s">
@@ -16603,617 +15842,384 @@
       <c r="C1" t="s">
         <v>19</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" s="2" customFormat="1">
+      <c r="E1" s="1" t="s">
+        <v>1013</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="2" customFormat="1">
       <c r="A2" s="2" t="s">
-        <v>601</v>
+        <v>244</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>602</v>
+        <v>245</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>601</v>
+        <v>244</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>607</v>
+        <v>250</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1032</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" s="2" customFormat="1">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="2" customFormat="1">
       <c r="A3" s="2" t="s">
-        <v>788</v>
+        <v>253</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>789</v>
+        <v>254</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>788</v>
+        <v>253</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" s="2" customFormat="1">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" s="2" customFormat="1">
       <c r="A4" s="2" t="s">
-        <v>796</v>
+        <v>259</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>797</v>
+        <v>260</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>796</v>
+        <v>259</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" s="4" customFormat="1">
-      <c r="A5" s="4" t="s">
-        <v>801</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>802</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>801</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>607</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>1030</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" s="2" customFormat="1">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" s="2" customFormat="1">
+      <c r="A5" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" s="2" customFormat="1">
       <c r="A6" s="2" t="s">
-        <v>808</v>
+        <v>268</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>809</v>
+        <v>269</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>808</v>
+        <v>268</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>1029</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" s="2" customFormat="1">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="2" customFormat="1">
       <c r="A7" s="2" t="s">
-        <v>833</v>
+        <v>272</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>834</v>
+        <v>273</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>833</v>
+        <v>272</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>1031</v>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="2" customFormat="1">
+      <c r="A8" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="2" customFormat="1" ht="16" thickBot="1">
+      <c r="A9" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" s="2" customFormat="1" ht="16" thickBot="1">
+      <c r="A10" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>1010</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" s="2" customFormat="1">
+      <c r="A11" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" s="4" customFormat="1">
+      <c r="A12" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" s="2" customFormat="1">
+      <c r="A13" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" s="2" customFormat="1">
+      <c r="A14" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" s="2" customFormat="1">
+      <c r="A15" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>871</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" s="2" customFormat="1">
+      <c r="A16" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" s="2" customFormat="1">
+      <c r="A17" s="2" t="s">
+        <v>903</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>904</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>903</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" s="4" customFormat="1">
+      <c r="A18" s="4" t="s">
+        <v>907</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>908</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>907</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" s="4" customFormat="1">
+      <c r="A19" s="4" t="s">
+        <v>911</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>911</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" s="2" customFormat="1">
+      <c r="A20" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" s="2" customFormat="1">
+      <c r="A21" s="2" t="s">
+        <v>946</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>947</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>946</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" s="2" customFormat="1">
+      <c r="A22" s="2" t="s">
+        <v>951</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>952</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>951</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" s="2" customFormat="1">
+      <c r="A23" s="2" t="s">
+        <v>958</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>958</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" s="2" customFormat="1">
+      <c r="A24" s="2" t="s">
+        <v>964</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>965</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>964</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" s="2" customFormat="1">
+      <c r="A25" s="2" t="s">
+        <v>981</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>982</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>981</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>250</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F2D37CA-29C3-BD49-9326-06CF486A4EFB}">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <cols>
-    <col min="5" max="5" width="57.83203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" s="4" customFormat="1">
-      <c r="A1" s="4" t="s">
-        <v>417</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>418</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>417</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>422</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>1048</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>1049</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" s="8" customFormat="1">
-      <c r="A2" s="8" t="s">
-        <v>574</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>575</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>574</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>422</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B4857D5-237B-E945-A0DB-32FAF0CE7CD3}">
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <cols>
-    <col min="4" max="4" width="18.33203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" s="8" customFormat="1">
-      <c r="A2" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" s="8" customFormat="1">
-      <c r="A3" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" s="8" customFormat="1">
-      <c r="A4" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="2" t="s">
-        <v>593</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>594</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>593</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA47AA37-095C-2D41-ADC5-D8C2D0281F2E}">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" s="1" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>433</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C270AD3-01ED-274B-829E-C282786A8465}">
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.5" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1">
-      <c r="A1" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>1026</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>1023</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" s="3" customFormat="1">
-      <c r="A2" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>206</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7511E3A-EAFE-814F-AE01-B1ED38B5D125}">
-  <dimension ref="A1:E15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="44.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="43.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.83203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" s="3" customFormat="1">
-      <c r="A2" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" s="2" customFormat="1">
-      <c r="A3" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" s="2" customFormat="1">
-      <c r="A4" s="2" t="s">
-        <v>628</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>629</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" s="2" customFormat="1">
-      <c r="A5" s="2" t="s">
-        <v>638</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>639</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>642</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" s="2" customFormat="1">
-      <c r="A6" s="2" t="s">
-        <v>695</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>696</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>695</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" s="2" customFormat="1">
-      <c r="A7" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>706</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" s="2" customFormat="1">
-      <c r="A8" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>714</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" s="2" customFormat="1">
-      <c r="A9" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>719</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" s="2" customFormat="1">
-      <c r="A10" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>722</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" s="2" customFormat="1">
-      <c r="A11" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>735</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" s="2" customFormat="1">
-      <c r="A12" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>741</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" s="2" customFormat="1">
-      <c r="A13" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>841</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" s="2" customFormat="1">
-      <c r="A14" s="2" t="s">
-        <v>695</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>890</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>695</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" s="2" customFormat="1">
-      <c r="A15" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>998</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>393</v>
-      </c>
-    </row>
-  </sheetData>
+  <autoFilter ref="A1:A1048461" xr:uid="{190D282D-A498-5040-B7ED-BB0A4708E39A}"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>